--- a/sources/table_normalization/xlsx/economy-table52.xlsx
+++ b/sources/table_normalization/xlsx/economy-table52.xlsx
@@ -957,37 +957,7 @@
     <cellStyle name="适中 2" xfId="11"/>
     <cellStyle name="链接单元格 2" xfId="15"/>
   </cellStyles>
-  <dxfs count="454">
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1001,2426 +971,6 @@
           <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -6958,10 +4508,10 @@
     <dataField name="% of Total" fld="13" showDataAs="percentOfTotal" baseField="24" baseItem="0" numFmtId="10"/>
   </dataFields>
   <formats count="8">
-    <format dxfId="453">
+    <format dxfId="7">
       <pivotArea type="all" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="452">
+    <format dxfId="6">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -6970,7 +4520,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="451">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -6980,7 +4530,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="450">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -6990,16 +4540,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="449">
+    <format dxfId="3">
       <pivotArea field="24" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="448">
+    <format dxfId="2">
       <pivotArea field="24" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="441">
+    <format dxfId="1">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="440">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -7304,7 +4854,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
